--- a/AAII_Financials/Yearly/PPERY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PPERY_YR_FIN.xlsx
@@ -1683,10 +1683,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4852700</v>
+        <v>4919300</v>
       </c>
       <c r="E42" s="3">
-        <v>6028200</v>
+        <v>6268100</v>
       </c>
       <c r="F42" s="3">
         <v>7178800</v>
@@ -1716,10 +1716,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2009400</v>
+        <v>1845000</v>
       </c>
       <c r="E43" s="3">
-        <v>1706900</v>
+        <v>1657100</v>
       </c>
       <c r="F43" s="3">
         <v>1842600</v>
@@ -1782,10 +1782,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1690900</v>
+        <v>1535300</v>
       </c>
       <c r="E45" s="3">
-        <v>1696100</v>
+        <v>1629300</v>
       </c>
       <c r="F45" s="3">
         <v>2126600</v>
@@ -1815,10 +1815,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>28939600</v>
+        <v>28686300</v>
       </c>
       <c r="E46" s="3">
-        <v>21234800</v>
+        <v>21358100</v>
       </c>
       <c r="F46" s="3">
         <v>22558400</v>
@@ -2013,10 +2013,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1277000</v>
+        <v>1530400</v>
       </c>
       <c r="E52" s="3">
-        <v>1511500</v>
+        <v>1388200</v>
       </c>
       <c r="F52" s="3">
         <v>1160200</v>
@@ -2175,10 +2175,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7558500</v>
+        <v>7507800</v>
       </c>
       <c r="E58" s="3">
-        <v>11552800</v>
+        <v>11526500</v>
       </c>
       <c r="F58" s="3">
         <v>6367900</v>
@@ -2208,10 +2208,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1599000</v>
+        <v>1771600</v>
       </c>
       <c r="E59" s="3">
-        <v>1172100</v>
+        <v>1450200</v>
       </c>
       <c r="F59" s="3">
         <v>1985900</v>
@@ -2241,10 +2241,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>126658100</v>
+        <v>126779900</v>
       </c>
       <c r="E60" s="3">
-        <v>110742400</v>
+        <v>110994200</v>
       </c>
       <c r="F60" s="3">
         <v>103757100</v>
@@ -2274,7 +2274,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9024400</v>
+        <v>9021700</v>
       </c>
       <c r="E61" s="3">
         <v>7024300</v>
@@ -2307,10 +2307,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>13450300</v>
+        <v>13331200</v>
       </c>
       <c r="E62" s="3">
-        <v>12809000</v>
+        <v>12557200</v>
       </c>
       <c r="F62" s="3">
         <v>12051800</v>
